--- a/projects/project-2/assignment/src/aircraft_data.xlsx
+++ b/projects/project-2/assignment/src/aircraft_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\FAA\Drupal\Airports\Engineering, Design, &amp; Construction\Aircraft Characteristics Database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\School\Fall 2026\Ontology-Engineering\Ontology-Tradecraft\projects\project-2\assignment\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3528D2D9-1EA8-4CE3-9F8C-0DF0E568D119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACF0AC0-AFD0-4162-B7C0-DF9F84B62E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{852B0E64-BCCC-407E-85AF-9EDDBE8136BD}"/>
+    <workbookView xWindow="67455" yWindow="2085" windowWidth="19050" windowHeight="15585" xr2:uid="{852B0E64-BCCC-407E-85AF-9EDDBE8136BD}"/>
   </bookViews>
   <sheets>
     <sheet name="ACD_Data" sheetId="1" r:id="rId1"/>
@@ -4437,7 +4437,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4453,6 +4453,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -4592,7 +4598,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4727,6 +4733,27 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6578,9 +6605,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6618,7 +6645,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6724,7 +6751,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6866,7 +6893,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6875,54 +6902,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B2C235D-FDEC-42F2-8FD4-154978FFF057}">
   <dimension ref="A1:BD389"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.77734375" style="18" customWidth="1"/>
-    <col min="2" max="2" width="31.44140625" style="18" customWidth="1"/>
-    <col min="3" max="3" width="25.77734375" style="18" customWidth="1"/>
-    <col min="4" max="4" width="67.6640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.44140625" style="18" customWidth="1"/>
-    <col min="6" max="6" width="24.44140625" style="18" customWidth="1"/>
-    <col min="7" max="7" width="15.77734375" style="18" customWidth="1"/>
-    <col min="8" max="8" width="16.44140625" style="18" customWidth="1"/>
-    <col min="9" max="9" width="18.6640625" style="18" customWidth="1"/>
+    <col min="1" max="1" width="13.81640625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="31.453125" style="18" customWidth="1"/>
+    <col min="3" max="3" width="25.81640625" style="18" customWidth="1"/>
+    <col min="4" max="4" width="67.6328125" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.453125" style="18" customWidth="1"/>
+    <col min="6" max="6" width="24.453125" style="18" customWidth="1"/>
+    <col min="7" max="7" width="15.81640625" style="18" customWidth="1"/>
+    <col min="8" max="8" width="16.453125" style="18" customWidth="1"/>
+    <col min="9" max="9" width="18.6328125" style="18" customWidth="1"/>
     <col min="10" max="10" width="19" style="18" customWidth="1"/>
-    <col min="11" max="12" width="9.109375" style="18"/>
-    <col min="13" max="13" width="24.6640625" style="18" customWidth="1"/>
+    <col min="11" max="12" width="9.08984375" style="18"/>
+    <col min="13" max="13" width="24.6328125" style="18" customWidth="1"/>
     <col min="14" max="14" width="32" style="18" customWidth="1"/>
-    <col min="15" max="15" width="32.33203125" style="18" customWidth="1"/>
-    <col min="16" max="16" width="43.77734375" style="42" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="32.36328125" style="18" customWidth="1"/>
+    <col min="16" max="16" width="43.81640625" style="42" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="35" style="42" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.44140625" style="42" customWidth="1"/>
+    <col min="18" max="18" width="12.453125" style="42" customWidth="1"/>
     <col min="19" max="19" width="26" style="42" customWidth="1"/>
-    <col min="20" max="20" width="16.44140625" style="42" customWidth="1"/>
-    <col min="21" max="21" width="28.33203125" style="42" customWidth="1"/>
-    <col min="22" max="22" width="23.77734375" style="42" customWidth="1"/>
-    <col min="23" max="23" width="23.33203125" style="43" customWidth="1"/>
+    <col min="20" max="20" width="16.453125" style="42" customWidth="1"/>
+    <col min="21" max="21" width="28.36328125" style="42" customWidth="1"/>
+    <col min="22" max="22" width="23.81640625" style="42" customWidth="1"/>
+    <col min="23" max="23" width="23.36328125" style="43" customWidth="1"/>
     <col min="24" max="24" width="22" style="43" customWidth="1"/>
-    <col min="25" max="25" width="21.109375" style="18" customWidth="1"/>
-    <col min="26" max="26" width="13.44140625" style="18" customWidth="1"/>
-    <col min="27" max="27" width="20.109375" style="42" customWidth="1"/>
-    <col min="28" max="28" width="17.44140625" style="18" customWidth="1"/>
-    <col min="29" max="29" width="15.33203125" style="18" customWidth="1"/>
-    <col min="30" max="30" width="15.44140625" style="18" customWidth="1"/>
-    <col min="31" max="31" width="32.33203125" style="23" customWidth="1"/>
-    <col min="32" max="32" width="36.109375" style="18" customWidth="1"/>
-    <col min="33" max="33" width="32.44140625" style="18" customWidth="1"/>
-    <col min="34" max="34" width="21.44140625" style="18" customWidth="1"/>
-    <col min="35" max="35" width="9.109375" style="18"/>
-    <col min="36" max="36" width="9.6640625" style="18" customWidth="1"/>
+    <col min="25" max="25" width="21.08984375" style="18" customWidth="1"/>
+    <col min="26" max="26" width="13.453125" style="18" customWidth="1"/>
+    <col min="27" max="27" width="20.08984375" style="42" customWidth="1"/>
+    <col min="28" max="28" width="17.453125" style="18" customWidth="1"/>
+    <col min="29" max="29" width="15.36328125" style="18" customWidth="1"/>
+    <col min="30" max="30" width="15.453125" style="18" customWidth="1"/>
+    <col min="31" max="31" width="32.36328125" style="23" customWidth="1"/>
+    <col min="32" max="32" width="36.08984375" style="18" customWidth="1"/>
+    <col min="33" max="33" width="32.453125" style="18" customWidth="1"/>
+    <col min="34" max="34" width="21.453125" style="18" customWidth="1"/>
+    <col min="35" max="35" width="9.08984375" style="18"/>
+    <col min="36" max="36" width="9.6328125" style="18" customWidth="1"/>
     <col min="37" max="37" width="16" style="18" customWidth="1"/>
     <col min="38" max="38" width="22" style="43" customWidth="1"/>
-    <col min="39" max="39" width="26.33203125" style="43" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="111.77734375" style="18" customWidth="1"/>
-    <col min="41" max="41" width="14.109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="42" max="47" width="9.109375" style="18"/>
-    <col min="48" max="48" width="52.44140625" style="18" customWidth="1"/>
-    <col min="49" max="16384" width="9.109375" style="18"/>
+    <col min="39" max="39" width="26.36328125" style="43" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="111.81640625" style="18" customWidth="1"/>
+    <col min="41" max="41" width="14.08984375" style="18" bestFit="1" customWidth="1"/>
+    <col min="42" max="47" width="9.08984375" style="18"/>
+    <col min="48" max="48" width="52.453125" style="18" customWidth="1"/>
+    <col min="49" max="16384" width="9.08984375" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -7047,7 +7074,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A2" s="29" t="s">
         <v>39</v>
       </c>
@@ -7156,7 +7183,7 @@
       <c r="AN2" s="19"/>
       <c r="AO2" s="20"/>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A3" s="29" t="s">
         <v>57</v>
       </c>
@@ -7265,7 +7292,7 @@
       <c r="AN3" s="19"/>
       <c r="AO3" s="20"/>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A4" s="29" t="s">
         <v>65</v>
       </c>
@@ -7376,118 +7403,118 @@
       </c>
       <c r="AO4" s="20"/>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A5" s="29" t="s">
+    <row r="5" spans="1:41" s="53" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="48">
         <v>2</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="H5" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20" t="s">
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="L5" s="20">
+      <c r="L5" s="48">
         <v>3</v>
       </c>
-      <c r="M5" s="20">
+      <c r="M5" s="48">
         <v>137</v>
       </c>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="30">
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49">
         <v>117.5</v>
       </c>
-      <c r="R5" s="30">
+      <c r="R5" s="49">
         <v>123.3</v>
       </c>
-      <c r="S5" s="30">
+      <c r="S5" s="49">
         <v>39.6</v>
       </c>
-      <c r="T5" s="30">
+      <c r="T5" s="49">
         <v>41.5</v>
       </c>
-      <c r="U5" s="30">
+      <c r="U5" s="49">
         <v>50.2</v>
       </c>
-      <c r="V5" s="30">
+      <c r="V5" s="49">
         <v>29.4</v>
       </c>
-      <c r="W5" s="31">
+      <c r="W5" s="50">
         <v>174165</v>
       </c>
-      <c r="X5" s="31">
+      <c r="X5" s="50">
         <v>148591</v>
       </c>
-      <c r="Y5" s="20" t="s">
+      <c r="Y5" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="Z5" s="20" t="s">
+      <c r="Z5" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="AA5" s="30">
+      <c r="AA5" s="49">
         <v>16358.3</v>
       </c>
-      <c r="AB5" s="20" t="s">
+      <c r="AB5" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="AC5" s="20" t="s">
+      <c r="AC5" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="AD5" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="AE5" s="20" t="s">
+      <c r="AD5" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE5" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="AF5" s="20" t="s">
+      <c r="AF5" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="AG5" s="20" t="s">
+      <c r="AG5" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="AH5" s="20"/>
-      <c r="AI5" s="20" t="s">
+      <c r="AH5" s="48"/>
+      <c r="AI5" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="AJ5" s="20">
+      <c r="AJ5" s="48">
         <v>7</v>
       </c>
-      <c r="AK5" s="20" t="s">
+      <c r="AK5" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="AL5" s="31">
+      <c r="AL5" s="50">
         <v>147</v>
       </c>
-      <c r="AM5" s="32">
+      <c r="AM5" s="51">
         <v>540276</v>
       </c>
-      <c r="AN5" s="19" t="s">
+      <c r="AN5" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="AO5" s="20"/>
+      <c r="AO5" s="48"/>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A6" s="29" t="s">
         <v>75</v>
       </c>
@@ -7598,7 +7625,7 @@
       </c>
       <c r="AO6" s="20"/>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A7" s="29" t="s">
         <v>78</v>
       </c>
@@ -7709,7 +7736,7 @@
       </c>
       <c r="AO7" s="20"/>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A8" s="29" t="s">
         <v>83</v>
       </c>
@@ -7820,7 +7847,7 @@
       </c>
       <c r="AO8" s="20"/>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A9" s="29" t="s">
         <v>86</v>
       </c>
@@ -7931,7 +7958,7 @@
       </c>
       <c r="AO9" s="20"/>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A10" s="29" t="s">
         <v>89</v>
       </c>
@@ -8042,7 +8069,7 @@
       </c>
       <c r="AO10" s="20"/>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A11" s="29" t="s">
         <v>92</v>
       </c>
@@ -8155,7 +8182,7 @@
       </c>
       <c r="AO11" s="20"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A12" s="29" t="s">
         <v>95</v>
       </c>
@@ -8268,7 +8295,7 @@
       </c>
       <c r="AO12" s="20"/>
     </row>
-    <row r="13" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:41" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="29" t="s">
         <v>98</v>
       </c>
@@ -8389,7 +8416,7 @@
       </c>
       <c r="AO13" s="20"/>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A14" s="29" t="s">
         <v>102</v>
       </c>
@@ -8500,7 +8527,7 @@
       </c>
       <c r="AO14" s="20"/>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A15" s="29" t="s">
         <v>107</v>
       </c>
@@ -8611,7 +8638,7 @@
       </c>
       <c r="AO15" s="20"/>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A16" s="29" t="s">
         <v>110</v>
       </c>
@@ -8720,7 +8747,7 @@
       <c r="AN16" s="19"/>
       <c r="AO16" s="20"/>
     </row>
-    <row r="17" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A17" s="29" t="s">
         <v>113</v>
       </c>
@@ -8829,7 +8856,7 @@
       <c r="AN17" s="19"/>
       <c r="AO17" s="20"/>
     </row>
-    <row r="18" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A18" s="29" t="s">
         <v>115</v>
       </c>
@@ -8940,7 +8967,7 @@
       </c>
       <c r="AO18" s="20"/>
     </row>
-    <row r="19" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A19" s="29" t="s">
         <v>118</v>
       </c>
@@ -9049,7 +9076,7 @@
       <c r="AN19" s="19"/>
       <c r="AO19" s="20"/>
     </row>
-    <row r="20" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A20" s="29" t="s">
         <v>122</v>
       </c>
@@ -9158,7 +9185,7 @@
       <c r="AN20" s="19"/>
       <c r="AO20" s="20"/>
     </row>
-    <row r="21" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A21" s="29" t="s">
         <v>125</v>
       </c>
@@ -9267,7 +9294,7 @@
       <c r="AN21" s="19"/>
       <c r="AO21" s="20"/>
     </row>
-    <row r="22" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A22" s="29" t="s">
         <v>129</v>
       </c>
@@ -9376,7 +9403,7 @@
       <c r="AN22" s="19"/>
       <c r="AO22" s="20"/>
     </row>
-    <row r="23" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A23" s="29" t="s">
         <v>132</v>
       </c>
@@ -9489,7 +9516,7 @@
         <v>45571</v>
       </c>
     </row>
-    <row r="24" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A24" s="29" t="s">
         <v>135</v>
       </c>
@@ -9602,7 +9629,7 @@
         <v>45571</v>
       </c>
     </row>
-    <row r="25" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A25" s="29" t="s">
         <v>139</v>
       </c>
@@ -9715,7 +9742,7 @@
         <v>45571</v>
       </c>
     </row>
-    <row r="26" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A26" s="29" t="s">
         <v>144</v>
       </c>
@@ -9824,7 +9851,7 @@
       <c r="AN26" s="19"/>
       <c r="AO26" s="20"/>
     </row>
-    <row r="27" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A27" s="29" t="s">
         <v>148</v>
       </c>
@@ -9933,7 +9960,7 @@
       <c r="AN27" s="19"/>
       <c r="AO27" s="20"/>
     </row>
-    <row r="28" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A28" s="29" t="s">
         <v>157</v>
       </c>
@@ -10045,7 +10072,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="29" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A29" s="29" t="s">
         <v>162</v>
       </c>
@@ -10154,7 +10181,7 @@
       <c r="AN29" s="19"/>
       <c r="AO29" s="20"/>
     </row>
-    <row r="30" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A30" s="29" t="s">
         <v>165</v>
       </c>
@@ -10263,7 +10290,7 @@
       <c r="AN30" s="19"/>
       <c r="AO30" s="20"/>
     </row>
-    <row r="31" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A31" s="29" t="s">
         <v>169</v>
       </c>
@@ -10372,7 +10399,7 @@
       <c r="AN31" s="19"/>
       <c r="AO31" s="20"/>
     </row>
-    <row r="32" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A32" s="29" t="s">
         <v>172</v>
       </c>
@@ -10481,7 +10508,7 @@
       <c r="AN32" s="19"/>
       <c r="AO32" s="20"/>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A33" s="29" t="s">
         <v>174</v>
       </c>
@@ -10590,7 +10617,7 @@
       <c r="AN33" s="19"/>
       <c r="AO33" s="20"/>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A34" s="29" t="s">
         <v>177</v>
       </c>
@@ -10699,7 +10726,7 @@
       <c r="AN34" s="19"/>
       <c r="AO34" s="20"/>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A35" s="29" t="s">
         <v>180</v>
       </c>
@@ -10808,7 +10835,7 @@
       <c r="AN35" s="19"/>
       <c r="AO35" s="20"/>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A36" s="29" t="s">
         <v>183</v>
       </c>
@@ -10917,7 +10944,7 @@
       <c r="AN36" s="19"/>
       <c r="AO36" s="20"/>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A37" s="29" t="s">
         <v>187</v>
       </c>
@@ -11026,7 +11053,7 @@
       <c r="AN37" s="19"/>
       <c r="AO37" s="20"/>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A38" s="29" t="s">
         <v>190</v>
       </c>
@@ -11135,7 +11162,7 @@
       <c r="AN38" s="19"/>
       <c r="AO38" s="20"/>
     </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A39" s="29" t="s">
         <v>194</v>
       </c>
@@ -11244,7 +11271,7 @@
       <c r="AN39" s="19"/>
       <c r="AO39" s="20"/>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A40" s="29" t="s">
         <v>197</v>
       </c>
@@ -11353,7 +11380,7 @@
       <c r="AN40" s="19"/>
       <c r="AO40" s="20"/>
     </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A41" s="29" t="s">
         <v>202</v>
       </c>
@@ -11462,7 +11489,7 @@
       <c r="AN41" s="19"/>
       <c r="AO41" s="20"/>
     </row>
-    <row r="42" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A42" s="29" t="s">
         <v>205</v>
       </c>
@@ -11571,7 +11598,7 @@
       <c r="AN42" s="19"/>
       <c r="AO42" s="20"/>
     </row>
-    <row r="43" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A43" s="29" t="s">
         <v>211</v>
       </c>
@@ -11680,7 +11707,7 @@
       <c r="AN43" s="19"/>
       <c r="AO43" s="20"/>
     </row>
-    <row r="44" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A44" s="29" t="s">
         <v>215</v>
       </c>
@@ -11789,7 +11816,7 @@
       <c r="AN44" s="19"/>
       <c r="AO44" s="20"/>
     </row>
-    <row r="45" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A45" s="29" t="s">
         <v>219</v>
       </c>
@@ -11898,7 +11925,7 @@
       <c r="AN45" s="19"/>
       <c r="AO45" s="20"/>
     </row>
-    <row r="46" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A46" s="29" t="s">
         <v>222</v>
       </c>
@@ -12007,7 +12034,7 @@
       <c r="AN46" s="19"/>
       <c r="AO46" s="20"/>
     </row>
-    <row r="47" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A47" s="29" t="s">
         <v>224</v>
       </c>
@@ -12116,7 +12143,7 @@
       <c r="AN47" s="19"/>
       <c r="AO47" s="20"/>
     </row>
-    <row r="48" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A48" s="29" t="s">
         <v>226</v>
       </c>
@@ -12225,7 +12252,7 @@
       <c r="AN48" s="19"/>
       <c r="AO48" s="20"/>
     </row>
-    <row r="49" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A49" s="29" t="s">
         <v>229</v>
       </c>
@@ -12334,7 +12361,7 @@
       <c r="AN49" s="19"/>
       <c r="AO49" s="20"/>
     </row>
-    <row r="50" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A50" s="29" t="s">
         <v>232</v>
       </c>
@@ -12443,7 +12470,7 @@
       <c r="AN50" s="19"/>
       <c r="AO50" s="20"/>
     </row>
-    <row r="51" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A51" s="29" t="s">
         <v>235</v>
       </c>
@@ -12552,7 +12579,7 @@
       <c r="AN51" s="19"/>
       <c r="AO51" s="20"/>
     </row>
-    <row r="52" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A52" s="29" t="s">
         <v>238</v>
       </c>
@@ -12661,7 +12688,7 @@
       <c r="AN52" s="19"/>
       <c r="AO52" s="20"/>
     </row>
-    <row r="53" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A53" s="29" t="s">
         <v>241</v>
       </c>
@@ -12770,7 +12797,7 @@
       <c r="AN53" s="19"/>
       <c r="AO53" s="20"/>
     </row>
-    <row r="54" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A54" s="29" t="s">
         <v>244</v>
       </c>
@@ -12879,7 +12906,7 @@
       <c r="AN54" s="19"/>
       <c r="AO54" s="20"/>
     </row>
-    <row r="55" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A55" s="29" t="s">
         <v>248</v>
       </c>
@@ -12988,7 +13015,7 @@
       <c r="AN55" s="19"/>
       <c r="AO55" s="20"/>
     </row>
-    <row r="56" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A56" s="29" t="s">
         <v>252</v>
       </c>
@@ -13107,7 +13134,7 @@
       </c>
       <c r="AO56" s="20"/>
     </row>
-    <row r="57" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A57" s="29" t="s">
         <v>255</v>
       </c>
@@ -13216,7 +13243,7 @@
       <c r="AN57" s="19"/>
       <c r="AO57" s="20"/>
     </row>
-    <row r="58" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A58" s="29" t="s">
         <v>258</v>
       </c>
@@ -13325,7 +13352,7 @@
       <c r="AN58" s="19"/>
       <c r="AO58" s="20"/>
     </row>
-    <row r="59" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A59" s="29" t="s">
         <v>261</v>
       </c>
@@ -13434,7 +13461,7 @@
       <c r="AN59" s="19"/>
       <c r="AO59" s="20"/>
     </row>
-    <row r="60" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A60" s="29" t="s">
         <v>265</v>
       </c>
@@ -13553,7 +13580,7 @@
       </c>
       <c r="AO60" s="20"/>
     </row>
-    <row r="61" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A61" s="29" t="s">
         <v>270</v>
       </c>
@@ -13672,7 +13699,7 @@
       </c>
       <c r="AO61" s="20"/>
     </row>
-    <row r="62" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A62" s="29" t="s">
         <v>273</v>
       </c>
@@ -13791,7 +13818,7 @@
       </c>
       <c r="AO62" s="20"/>
     </row>
-    <row r="63" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A63" s="29" t="s">
         <v>276</v>
       </c>
@@ -13900,7 +13927,7 @@
       <c r="AN63" s="19"/>
       <c r="AO63" s="20"/>
     </row>
-    <row r="64" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A64" s="29" t="s">
         <v>280</v>
       </c>
@@ -14009,7 +14036,7 @@
       <c r="AN64" s="19"/>
       <c r="AO64" s="20"/>
     </row>
-    <row r="65" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A65" s="29" t="s">
         <v>283</v>
       </c>
@@ -14118,7 +14145,7 @@
       <c r="AN65" s="19"/>
       <c r="AO65" s="20"/>
     </row>
-    <row r="66" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A66" s="29" t="s">
         <v>286</v>
       </c>
@@ -14227,7 +14254,7 @@
       <c r="AN66" s="19"/>
       <c r="AO66" s="20"/>
     </row>
-    <row r="67" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A67" s="29" t="s">
         <v>289</v>
       </c>
@@ -14338,7 +14365,7 @@
       </c>
       <c r="AO67" s="20"/>
     </row>
-    <row r="68" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A68" s="29" t="s">
         <v>292</v>
       </c>
@@ -14447,7 +14474,7 @@
       <c r="AN68" s="19"/>
       <c r="AO68" s="20"/>
     </row>
-    <row r="69" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A69" s="29" t="s">
         <v>295</v>
       </c>
@@ -14558,7 +14585,7 @@
       <c r="AN69" s="19"/>
       <c r="AO69" s="20"/>
     </row>
-    <row r="70" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A70" s="29" t="s">
         <v>298</v>
       </c>
@@ -14669,7 +14696,7 @@
       </c>
       <c r="AO70" s="20"/>
     </row>
-    <row r="71" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A71" s="29" t="s">
         <v>301</v>
       </c>
@@ -14782,7 +14809,7 @@
       </c>
       <c r="AO71" s="20"/>
     </row>
-    <row r="72" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A72" s="29" t="s">
         <v>304</v>
       </c>
@@ -14893,7 +14920,7 @@
       </c>
       <c r="AO72" s="20"/>
     </row>
-    <row r="73" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A73" s="29" t="s">
         <v>307</v>
       </c>
@@ -15004,7 +15031,7 @@
       </c>
       <c r="AO73" s="20"/>
     </row>
-    <row r="74" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A74" s="29" t="s">
         <v>310</v>
       </c>
@@ -15117,7 +15144,7 @@
       </c>
       <c r="AO74" s="20"/>
     </row>
-    <row r="75" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A75" s="29" t="s">
         <v>313</v>
       </c>
@@ -15230,7 +15257,7 @@
       </c>
       <c r="AO75" s="20"/>
     </row>
-    <row r="76" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A76" s="29" t="s">
         <v>316</v>
       </c>
@@ -15351,7 +15378,7 @@
       </c>
       <c r="AO76" s="20"/>
     </row>
-    <row r="77" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A77" s="29" t="s">
         <v>319</v>
       </c>
@@ -15472,7 +15499,7 @@
       </c>
       <c r="AO77" s="20"/>
     </row>
-    <row r="78" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A78" s="29" t="s">
         <v>322</v>
       </c>
@@ -15581,7 +15608,7 @@
       <c r="AN78" s="19"/>
       <c r="AO78" s="20"/>
     </row>
-    <row r="79" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A79" s="29" t="s">
         <v>325</v>
       </c>
@@ -15690,7 +15717,7 @@
       <c r="AN79" s="19"/>
       <c r="AO79" s="20"/>
     </row>
-    <row r="80" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A80" s="29" t="s">
         <v>328</v>
       </c>
@@ -15799,7 +15826,7 @@
       <c r="AN80" s="19"/>
       <c r="AO80" s="20"/>
     </row>
-    <row r="81" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A81" s="29" t="s">
         <v>331</v>
       </c>
@@ -15910,7 +15937,7 @@
       </c>
       <c r="AO81" s="20"/>
     </row>
-    <row r="82" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A82" s="29" t="s">
         <v>334</v>
       </c>
@@ -16021,7 +16048,7 @@
       </c>
       <c r="AO82" s="20"/>
     </row>
-    <row r="83" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A83" s="29" t="s">
         <v>337</v>
       </c>
@@ -16132,7 +16159,7 @@
       <c r="AN83" s="19"/>
       <c r="AO83" s="20"/>
     </row>
-    <row r="84" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A84" s="29" t="s">
         <v>340</v>
       </c>
@@ -16243,7 +16270,7 @@
       <c r="AN84" s="19"/>
       <c r="AO84" s="20"/>
     </row>
-    <row r="85" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A85" s="29" t="s">
         <v>343</v>
       </c>
@@ -16352,7 +16379,7 @@
       <c r="AN85" s="19"/>
       <c r="AO85" s="20"/>
     </row>
-    <row r="86" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A86" s="29" t="s">
         <v>346</v>
       </c>
@@ -16463,7 +16490,7 @@
       <c r="AN86" s="19"/>
       <c r="AO86" s="20"/>
     </row>
-    <row r="87" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A87" s="29" t="s">
         <v>349</v>
       </c>
@@ -16572,7 +16599,7 @@
       <c r="AN87" s="19"/>
       <c r="AO87" s="20"/>
     </row>
-    <row r="88" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A88" s="29" t="s">
         <v>352</v>
       </c>
@@ -16683,7 +16710,7 @@
       </c>
       <c r="AO88" s="20"/>
     </row>
-    <row r="89" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A89" s="29" t="s">
         <v>355</v>
       </c>
@@ -16794,7 +16821,7 @@
       </c>
       <c r="AO89" s="20"/>
     </row>
-    <row r="90" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A90" s="29" t="s">
         <v>358</v>
       </c>
@@ -16905,7 +16932,7 @@
       </c>
       <c r="AO90" s="20"/>
     </row>
-    <row r="91" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A91" s="29" t="s">
         <v>361</v>
       </c>
@@ -17016,7 +17043,7 @@
       </c>
       <c r="AO91" s="20"/>
     </row>
-    <row r="92" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A92" s="29" t="s">
         <v>363</v>
       </c>
@@ -17127,7 +17154,7 @@
       </c>
       <c r="AO92" s="20"/>
     </row>
-    <row r="93" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A93" s="29" t="s">
         <v>366</v>
       </c>
@@ -17238,7 +17265,7 @@
       </c>
       <c r="AO93" s="20"/>
     </row>
-    <row r="94" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A94" s="29" t="s">
         <v>369</v>
       </c>
@@ -17357,7 +17384,7 @@
       </c>
       <c r="AO94" s="20"/>
     </row>
-    <row r="95" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A95" s="29" t="s">
         <v>373</v>
       </c>
@@ -17476,7 +17503,7 @@
       </c>
       <c r="AO95" s="20"/>
     </row>
-    <row r="96" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A96" s="29" t="s">
         <v>376</v>
       </c>
@@ -17587,7 +17614,7 @@
       </c>
       <c r="AO96" s="20"/>
     </row>
-    <row r="97" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A97" s="29" t="s">
         <v>380</v>
       </c>
@@ -17696,7 +17723,7 @@
       <c r="AN97" s="19"/>
       <c r="AO97" s="20"/>
     </row>
-    <row r="98" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A98" s="29" t="s">
         <v>384</v>
       </c>
@@ -17807,7 +17834,7 @@
       </c>
       <c r="AO98" s="20"/>
     </row>
-    <row r="99" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A99" s="29" t="s">
         <v>388</v>
       </c>
@@ -17916,7 +17943,7 @@
       <c r="AN99" s="19"/>
       <c r="AO99" s="20"/>
     </row>
-    <row r="100" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A100" s="29" t="s">
         <v>391</v>
       </c>
@@ -18025,7 +18052,7 @@
       <c r="AN100" s="19"/>
       <c r="AO100" s="20"/>
     </row>
-    <row r="101" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A101" s="29" t="s">
         <v>394</v>
       </c>
@@ -18134,7 +18161,7 @@
       <c r="AN101" s="19"/>
       <c r="AO101" s="20"/>
     </row>
-    <row r="102" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A102" s="29" t="s">
         <v>397</v>
       </c>
@@ -18243,7 +18270,7 @@
       <c r="AN102" s="19"/>
       <c r="AO102" s="20"/>
     </row>
-    <row r="103" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A103" s="29" t="s">
         <v>400</v>
       </c>
@@ -18354,7 +18381,7 @@
       </c>
       <c r="AO103" s="20"/>
     </row>
-    <row r="104" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A104" s="29" t="s">
         <v>403</v>
       </c>
@@ -18463,7 +18490,7 @@
       <c r="AN104" s="19"/>
       <c r="AO104" s="20"/>
     </row>
-    <row r="105" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A105" s="29" t="s">
         <v>406</v>
       </c>
@@ -18572,7 +18599,7 @@
       <c r="AN105" s="19"/>
       <c r="AO105" s="20"/>
     </row>
-    <row r="106" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A106" s="29" t="s">
         <v>408</v>
       </c>
@@ -18683,7 +18710,7 @@
       </c>
       <c r="AO106" s="20"/>
     </row>
-    <row r="107" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A107" s="29" t="s">
         <v>412</v>
       </c>
@@ -18792,7 +18819,7 @@
       <c r="AN107" s="19"/>
       <c r="AO107" s="20"/>
     </row>
-    <row r="108" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A108" s="29" t="s">
         <v>415</v>
       </c>
@@ -18901,7 +18928,7 @@
       <c r="AN108" s="19"/>
       <c r="AO108" s="20"/>
     </row>
-    <row r="109" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A109" s="29" t="s">
         <v>418</v>
       </c>
@@ -19010,7 +19037,7 @@
       <c r="AN109" s="19"/>
       <c r="AO109" s="20"/>
     </row>
-    <row r="110" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A110" s="29" t="s">
         <v>421</v>
       </c>
@@ -19119,7 +19146,7 @@
       <c r="AN110" s="19"/>
       <c r="AO110" s="20"/>
     </row>
-    <row r="111" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A111" s="29" t="s">
         <v>425</v>
       </c>
@@ -19228,7 +19255,7 @@
       <c r="AN111" s="19"/>
       <c r="AO111" s="20"/>
     </row>
-    <row r="112" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A112" s="29" t="s">
         <v>428</v>
       </c>
@@ -19337,7 +19364,7 @@
       <c r="AN112" s="19"/>
       <c r="AO112" s="20"/>
     </row>
-    <row r="113" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A113" s="29" t="s">
         <v>431</v>
       </c>
@@ -19446,7 +19473,7 @@
       <c r="AN113" s="19"/>
       <c r="AO113" s="20"/>
     </row>
-    <row r="114" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A114" s="29" t="s">
         <v>434</v>
       </c>
@@ -19555,7 +19582,7 @@
       <c r="AN114" s="19"/>
       <c r="AO114" s="20"/>
     </row>
-    <row r="115" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A115" s="29" t="s">
         <v>436</v>
       </c>
@@ -19664,7 +19691,7 @@
       <c r="AN115" s="19"/>
       <c r="AO115" s="20"/>
     </row>
-    <row r="116" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A116" s="29" t="s">
         <v>438</v>
       </c>
@@ -19773,7 +19800,7 @@
       <c r="AN116" s="19"/>
       <c r="AO116" s="20"/>
     </row>
-    <row r="117" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A117" s="29" t="s">
         <v>440</v>
       </c>
@@ -19882,7 +19909,7 @@
       <c r="AN117" s="19"/>
       <c r="AO117" s="20"/>
     </row>
-    <row r="118" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A118" s="29" t="s">
         <v>443</v>
       </c>
@@ -19991,7 +20018,7 @@
       <c r="AN118" s="19"/>
       <c r="AO118" s="20"/>
     </row>
-    <row r="119" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A119" s="29" t="s">
         <v>445</v>
       </c>
@@ -20100,7 +20127,7 @@
       <c r="AN119" s="19"/>
       <c r="AO119" s="20"/>
     </row>
-    <row r="120" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A120" s="29" t="s">
         <v>448</v>
       </c>
@@ -20209,7 +20236,7 @@
       <c r="AN120" s="19"/>
       <c r="AO120" s="20"/>
     </row>
-    <row r="121" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A121" s="29" t="s">
         <v>451</v>
       </c>
@@ -20318,7 +20345,7 @@
       <c r="AN121" s="19"/>
       <c r="AO121" s="20"/>
     </row>
-    <row r="122" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A122" s="29" t="s">
         <v>454</v>
       </c>
@@ -20427,7 +20454,7 @@
       <c r="AN122" s="19"/>
       <c r="AO122" s="20"/>
     </row>
-    <row r="123" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A123" s="29" t="s">
         <v>457</v>
       </c>
@@ -20536,7 +20563,7 @@
       <c r="AN123" s="19"/>
       <c r="AO123" s="20"/>
     </row>
-    <row r="124" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A124" s="29" t="s">
         <v>460</v>
       </c>
@@ -20645,7 +20672,7 @@
       <c r="AN124" s="19"/>
       <c r="AO124" s="20"/>
     </row>
-    <row r="125" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A125" s="29" t="s">
         <v>464</v>
       </c>
@@ -20754,7 +20781,7 @@
       <c r="AN125" s="19"/>
       <c r="AO125" s="20"/>
     </row>
-    <row r="126" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A126" s="29" t="s">
         <v>466</v>
       </c>
@@ -20863,7 +20890,7 @@
       <c r="AN126" s="19"/>
       <c r="AO126" s="20"/>
     </row>
-    <row r="127" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A127" s="29" t="s">
         <v>468</v>
       </c>
@@ -20972,7 +20999,7 @@
       <c r="AN127" s="19"/>
       <c r="AO127" s="20"/>
     </row>
-    <row r="128" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A128" s="29" t="s">
         <v>471</v>
       </c>
@@ -21081,7 +21108,7 @@
       <c r="AN128" s="19"/>
       <c r="AO128" s="20"/>
     </row>
-    <row r="129" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A129" s="29" t="s">
         <v>474</v>
       </c>
@@ -21190,7 +21217,7 @@
       <c r="AN129" s="19"/>
       <c r="AO129" s="20"/>
     </row>
-    <row r="130" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A130" s="29" t="s">
         <v>478</v>
       </c>
@@ -21299,7 +21326,7 @@
       <c r="AN130" s="19"/>
       <c r="AO130" s="20"/>
     </row>
-    <row r="131" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A131" s="29" t="s">
         <v>480</v>
       </c>
@@ -21408,7 +21435,7 @@
       <c r="AN131" s="19"/>
       <c r="AO131" s="20"/>
     </row>
-    <row r="132" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A132" s="29" t="s">
         <v>482</v>
       </c>
@@ -21517,7 +21544,7 @@
       <c r="AN132" s="19"/>
       <c r="AO132" s="20"/>
     </row>
-    <row r="133" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A133" s="29" t="s">
         <v>484</v>
       </c>
@@ -21626,7 +21653,7 @@
       <c r="AN133" s="19"/>
       <c r="AO133" s="20"/>
     </row>
-    <row r="134" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A134" s="29" t="s">
         <v>488</v>
       </c>
@@ -21735,7 +21762,7 @@
       <c r="AN134" s="19"/>
       <c r="AO134" s="20"/>
     </row>
-    <row r="135" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A135" s="29" t="s">
         <v>491</v>
       </c>
@@ -21844,7 +21871,7 @@
       <c r="AN135" s="19"/>
       <c r="AO135" s="20"/>
     </row>
-    <row r="136" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A136" s="29" t="s">
         <v>495</v>
       </c>
@@ -21953,7 +21980,7 @@
       <c r="AN136" s="19"/>
       <c r="AO136" s="20"/>
     </row>
-    <row r="137" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A137" s="29" t="s">
         <v>497</v>
       </c>
@@ -22062,7 +22089,7 @@
       <c r="AN137" s="19"/>
       <c r="AO137" s="20"/>
     </row>
-    <row r="138" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A138" s="29" t="s">
         <v>500</v>
       </c>
@@ -22171,7 +22198,7 @@
       <c r="AN138" s="19"/>
       <c r="AO138" s="20"/>
     </row>
-    <row r="139" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A139" s="29" t="s">
         <v>503</v>
       </c>
@@ -22280,7 +22307,7 @@
       <c r="AN139" s="19"/>
       <c r="AO139" s="20"/>
     </row>
-    <row r="140" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A140" s="29" t="s">
         <v>505</v>
       </c>
@@ -22389,7 +22416,7 @@
       <c r="AN140" s="19"/>
       <c r="AO140" s="20"/>
     </row>
-    <row r="141" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A141" s="29" t="s">
         <v>508</v>
       </c>
@@ -22498,7 +22525,7 @@
       <c r="AN141" s="19"/>
       <c r="AO141" s="20"/>
     </row>
-    <row r="142" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A142" s="29" t="s">
         <v>511</v>
       </c>
@@ -22607,7 +22634,7 @@
       <c r="AN142" s="19"/>
       <c r="AO142" s="20"/>
     </row>
-    <row r="143" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A143" s="29" t="s">
         <v>513</v>
       </c>
@@ -22716,7 +22743,7 @@
       <c r="AN143" s="19"/>
       <c r="AO143" s="20"/>
     </row>
-    <row r="144" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A144" s="29" t="s">
         <v>516</v>
       </c>
@@ -22825,7 +22852,7 @@
       <c r="AN144" s="19"/>
       <c r="AO144" s="20"/>
     </row>
-    <row r="145" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A145" s="29" t="s">
         <v>518</v>
       </c>
@@ -22934,7 +22961,7 @@
       <c r="AN145" s="19"/>
       <c r="AO145" s="20"/>
     </row>
-    <row r="146" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A146" s="29" t="s">
         <v>521</v>
       </c>
@@ -23043,7 +23070,7 @@
       <c r="AN146" s="19"/>
       <c r="AO146" s="20"/>
     </row>
-    <row r="147" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A147" s="29" t="s">
         <v>525</v>
       </c>
@@ -23152,7 +23179,7 @@
       <c r="AN147" s="19"/>
       <c r="AO147" s="20"/>
     </row>
-    <row r="148" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A148" s="29" t="s">
         <v>528</v>
       </c>
@@ -23261,7 +23288,7 @@
       <c r="AN148" s="19"/>
       <c r="AO148" s="20"/>
     </row>
-    <row r="149" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A149" s="29" t="s">
         <v>531</v>
       </c>
@@ -23370,7 +23397,7 @@
       <c r="AN149" s="19"/>
       <c r="AO149" s="20"/>
     </row>
-    <row r="150" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A150" s="29" t="s">
         <v>535</v>
       </c>
@@ -23479,7 +23506,7 @@
       <c r="AN150" s="19"/>
       <c r="AO150" s="20"/>
     </row>
-    <row r="151" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A151" s="29" t="s">
         <v>538</v>
       </c>
@@ -23590,7 +23617,7 @@
       </c>
       <c r="AO151" s="20"/>
     </row>
-    <row r="152" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A152" s="29" t="s">
         <v>541</v>
       </c>
@@ -23701,7 +23728,7 @@
       </c>
       <c r="AO152" s="20"/>
     </row>
-    <row r="153" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A153" s="29" t="s">
         <v>543</v>
       </c>
@@ -23812,7 +23839,7 @@
       </c>
       <c r="AO153" s="20"/>
     </row>
-    <row r="154" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A154" s="29" t="s">
         <v>545</v>
       </c>
@@ -23923,7 +23950,7 @@
       </c>
       <c r="AO154" s="20"/>
     </row>
-    <row r="155" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A155" s="29" t="s">
         <v>548</v>
       </c>
@@ -24032,7 +24059,7 @@
       <c r="AN155" s="19"/>
       <c r="AO155" s="20"/>
     </row>
-    <row r="156" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A156" s="29" t="s">
         <v>551</v>
       </c>
@@ -24141,7 +24168,7 @@
       <c r="AN156" s="19"/>
       <c r="AO156" s="20"/>
     </row>
-    <row r="157" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A157" s="29" t="s">
         <v>555</v>
       </c>
@@ -24250,7 +24277,7 @@
       <c r="AN157" s="19"/>
       <c r="AO157" s="20"/>
     </row>
-    <row r="158" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A158" s="29" t="s">
         <v>558</v>
       </c>
@@ -24359,7 +24386,7 @@
       <c r="AN158" s="19"/>
       <c r="AO158" s="20"/>
     </row>
-    <row r="159" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A159" s="29" t="s">
         <v>560</v>
       </c>
@@ -24468,7 +24495,7 @@
       <c r="AN159" s="19"/>
       <c r="AO159" s="20"/>
     </row>
-    <row r="160" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A160" s="29" t="s">
         <v>562</v>
       </c>
@@ -24577,7 +24604,7 @@
       <c r="AN160" s="19"/>
       <c r="AO160" s="20"/>
     </row>
-    <row r="161" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A161" s="29" t="s">
         <v>565</v>
       </c>
@@ -24686,7 +24713,7 @@
       <c r="AN161" s="19"/>
       <c r="AO161" s="20"/>
     </row>
-    <row r="162" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A162" s="29" t="s">
         <v>568</v>
       </c>
@@ -24795,7 +24822,7 @@
       <c r="AN162" s="19"/>
       <c r="AO162" s="20"/>
     </row>
-    <row r="163" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A163" s="29" t="s">
         <v>570</v>
       </c>
@@ -24904,7 +24931,7 @@
       <c r="AN163" s="19"/>
       <c r="AO163" s="20"/>
     </row>
-    <row r="164" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A164" s="29" t="s">
         <v>573</v>
       </c>
@@ -25013,7 +25040,7 @@
       <c r="AN164" s="19"/>
       <c r="AO164" s="20"/>
     </row>
-    <row r="165" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A165" s="29" t="s">
         <v>576</v>
       </c>
@@ -25122,7 +25149,7 @@
       <c r="AN165" s="19"/>
       <c r="AO165" s="20"/>
     </row>
-    <row r="166" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A166" s="29" t="s">
         <v>578</v>
       </c>
@@ -25231,7 +25258,7 @@
       <c r="AN166" s="19"/>
       <c r="AO166" s="20"/>
     </row>
-    <row r="167" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A167" s="29" t="s">
         <v>581</v>
       </c>
@@ -25342,7 +25369,7 @@
       </c>
       <c r="AO167" s="20"/>
     </row>
-    <row r="168" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A168" s="29" t="s">
         <v>585</v>
       </c>
@@ -25453,7 +25480,7 @@
       </c>
       <c r="AO168" s="20"/>
     </row>
-    <row r="169" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A169" s="29" t="s">
         <v>588</v>
       </c>
@@ -25564,7 +25591,7 @@
       </c>
       <c r="AO169" s="20"/>
     </row>
-    <row r="170" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A170" s="29" t="s">
         <v>590</v>
       </c>
@@ -25675,7 +25702,7 @@
       </c>
       <c r="AO170" s="20"/>
     </row>
-    <row r="171" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A171" s="29" t="s">
         <v>593</v>
       </c>
@@ -25784,7 +25811,7 @@
       <c r="AN171" s="19"/>
       <c r="AO171" s="20"/>
     </row>
-    <row r="172" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A172" s="29" t="s">
         <v>595</v>
       </c>
@@ -25895,7 +25922,7 @@
       </c>
       <c r="AO172" s="20"/>
     </row>
-    <row r="173" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A173" s="29" t="s">
         <v>599</v>
       </c>
@@ -26006,7 +26033,7 @@
       </c>
       <c r="AO173" s="20"/>
     </row>
-    <row r="174" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A174" s="29" t="s">
         <v>602</v>
       </c>
@@ -26117,7 +26144,7 @@
         <v>45491</v>
       </c>
     </row>
-    <row r="175" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A175" s="29" t="s">
         <v>604</v>
       </c>
@@ -26228,7 +26255,7 @@
       </c>
       <c r="AO175" s="20"/>
     </row>
-    <row r="176" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A176" s="29" t="s">
         <v>607</v>
       </c>
@@ -26339,7 +26366,7 @@
       </c>
       <c r="AO176" s="20"/>
     </row>
-    <row r="177" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A177" s="29" t="s">
         <v>610</v>
       </c>
@@ -26448,7 +26475,7 @@
       <c r="AN177" s="19"/>
       <c r="AO177" s="20"/>
     </row>
-    <row r="178" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A178" s="29" t="s">
         <v>613</v>
       </c>
@@ -26559,7 +26586,7 @@
       </c>
       <c r="AO178" s="20"/>
     </row>
-    <row r="179" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A179" s="29" t="s">
         <v>615</v>
       </c>
@@ -26670,7 +26697,7 @@
       </c>
       <c r="AO179" s="20"/>
     </row>
-    <row r="180" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A180" s="29" t="s">
         <v>618</v>
       </c>
@@ -26781,7 +26808,7 @@
       </c>
       <c r="AO180" s="20"/>
     </row>
-    <row r="181" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A181" s="29" t="s">
         <v>620</v>
       </c>
@@ -26890,7 +26917,7 @@
       <c r="AN181" s="19"/>
       <c r="AO181" s="20"/>
     </row>
-    <row r="182" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A182" s="29" t="s">
         <v>622</v>
       </c>
@@ -27001,7 +27028,7 @@
       </c>
       <c r="AO182" s="20"/>
     </row>
-    <row r="183" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A183" s="29" t="s">
         <v>624</v>
       </c>
@@ -27110,7 +27137,7 @@
       <c r="AN183" s="19"/>
       <c r="AO183" s="20"/>
     </row>
-    <row r="184" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A184" s="29" t="s">
         <v>627</v>
       </c>
@@ -27219,7 +27246,7 @@
       <c r="AN184" s="19"/>
       <c r="AO184" s="20"/>
     </row>
-    <row r="185" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A185" s="29" t="s">
         <v>630</v>
       </c>
@@ -27328,7 +27355,7 @@
       <c r="AN185" s="19"/>
       <c r="AO185" s="20"/>
     </row>
-    <row r="186" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A186" s="29" t="s">
         <v>633</v>
       </c>
@@ -27437,7 +27464,7 @@
       <c r="AN186" s="19"/>
       <c r="AO186" s="20"/>
     </row>
-    <row r="187" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A187" s="29" t="s">
         <v>636</v>
       </c>
@@ -27548,7 +27575,7 @@
       </c>
       <c r="AO187" s="20"/>
     </row>
-    <row r="188" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A188" s="29" t="s">
         <v>640</v>
       </c>
@@ -27659,7 +27686,7 @@
       </c>
       <c r="AO188" s="20"/>
     </row>
-    <row r="189" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A189" s="29" t="s">
         <v>642</v>
       </c>
@@ -27768,7 +27795,7 @@
       <c r="AN189" s="19"/>
       <c r="AO189" s="20"/>
     </row>
-    <row r="190" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A190" s="29" t="s">
         <v>646</v>
       </c>
@@ -27879,7 +27906,7 @@
       </c>
       <c r="AO190" s="20"/>
     </row>
-    <row r="191" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A191" s="29" t="s">
         <v>649</v>
       </c>
@@ -27990,7 +28017,7 @@
       </c>
       <c r="AO191" s="20"/>
     </row>
-    <row r="192" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A192" s="29" t="s">
         <v>651</v>
       </c>
@@ -28099,7 +28126,7 @@
       <c r="AN192" s="19"/>
       <c r="AO192" s="20"/>
     </row>
-    <row r="193" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A193" s="29" t="s">
         <v>655</v>
       </c>
@@ -28208,7 +28235,7 @@
       <c r="AN193" s="19"/>
       <c r="AO193" s="20"/>
     </row>
-    <row r="194" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A194" s="29" t="s">
         <v>658</v>
       </c>
@@ -28317,7 +28344,7 @@
       <c r="AN194" s="19"/>
       <c r="AO194" s="20"/>
     </row>
-    <row r="195" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A195" s="29" t="s">
         <v>662</v>
       </c>
@@ -28428,7 +28455,7 @@
       </c>
       <c r="AO195" s="20"/>
     </row>
-    <row r="196" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A196" s="29" t="s">
         <v>665</v>
       </c>
@@ -28539,7 +28566,7 @@
       </c>
       <c r="AO196" s="20"/>
     </row>
-    <row r="197" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A197" s="29" t="s">
         <v>668</v>
       </c>
@@ -28650,7 +28677,7 @@
       </c>
       <c r="AO197" s="20"/>
     </row>
-    <row r="198" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A198" s="29" t="s">
         <v>671</v>
       </c>
@@ -28769,7 +28796,7 @@
       </c>
       <c r="AO198" s="20"/>
     </row>
-    <row r="199" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A199" s="29" t="s">
         <v>675</v>
       </c>
@@ -28878,7 +28905,7 @@
       <c r="AN199" s="19"/>
       <c r="AO199" s="20"/>
     </row>
-    <row r="200" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A200" s="29" t="s">
         <v>678</v>
       </c>
@@ -28987,7 +29014,7 @@
       <c r="AN200" s="19"/>
       <c r="AO200" s="20"/>
     </row>
-    <row r="201" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A201" s="29" t="s">
         <v>682</v>
       </c>
@@ -29096,7 +29123,7 @@
       <c r="AN201" s="19"/>
       <c r="AO201" s="20"/>
     </row>
-    <row r="202" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A202" s="29" t="s">
         <v>686</v>
       </c>
@@ -29207,7 +29234,7 @@
       </c>
       <c r="AO202" s="20"/>
     </row>
-    <row r="203" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A203" s="29" t="s">
         <v>690</v>
       </c>
@@ -29316,7 +29343,7 @@
       <c r="AN203" s="19"/>
       <c r="AO203" s="20"/>
     </row>
-    <row r="204" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A204" s="29" t="s">
         <v>694</v>
       </c>
@@ -29425,7 +29452,7 @@
       <c r="AN204" s="19"/>
       <c r="AO204" s="20"/>
     </row>
-    <row r="205" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A205" s="29" t="s">
         <v>697</v>
       </c>
@@ -29534,7 +29561,7 @@
       <c r="AN205" s="19"/>
       <c r="AO205" s="20"/>
     </row>
-    <row r="206" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A206" s="29" t="s">
         <v>701</v>
       </c>
@@ -29645,7 +29672,7 @@
       </c>
       <c r="AO206" s="20"/>
     </row>
-    <row r="207" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A207" s="29" t="s">
         <v>705</v>
       </c>
@@ -29756,7 +29783,7 @@
       </c>
       <c r="AO207" s="20"/>
     </row>
-    <row r="208" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A208" s="29" t="s">
         <v>1412</v>
       </c>
@@ -29865,7 +29892,7 @@
         <v>45517</v>
       </c>
     </row>
-    <row r="209" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A209" s="29" t="s">
         <v>708</v>
       </c>
@@ -29974,7 +30001,7 @@
       <c r="AN209" s="19"/>
       <c r="AO209" s="20"/>
     </row>
-    <row r="210" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A210" s="29" t="s">
         <v>711</v>
       </c>
@@ -30083,7 +30110,7 @@
       <c r="AN210" s="19"/>
       <c r="AO210" s="20"/>
     </row>
-    <row r="211" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A211" s="29" t="s">
         <v>714</v>
       </c>
@@ -30194,7 +30221,7 @@
       </c>
       <c r="AO211" s="20"/>
     </row>
-    <row r="212" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A212" s="29" t="s">
         <v>717</v>
       </c>
@@ -30305,7 +30332,7 @@
       </c>
       <c r="AO212" s="20"/>
     </row>
-    <row r="213" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A213" s="29" t="s">
         <v>720</v>
       </c>
@@ -30416,7 +30443,7 @@
       </c>
       <c r="AO213" s="20"/>
     </row>
-    <row r="214" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A214" s="29" t="s">
         <v>723</v>
       </c>
@@ -30527,7 +30554,7 @@
       </c>
       <c r="AO214" s="20"/>
     </row>
-    <row r="215" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A215" s="29" t="s">
         <v>727</v>
       </c>
@@ -30638,7 +30665,7 @@
       </c>
       <c r="AO215" s="20"/>
     </row>
-    <row r="216" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A216" s="29" t="s">
         <v>730</v>
       </c>
@@ -30749,7 +30776,7 @@
       </c>
       <c r="AO216" s="20"/>
     </row>
-    <row r="217" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A217" s="29" t="s">
         <v>733</v>
       </c>
@@ -30860,7 +30887,7 @@
       </c>
       <c r="AO217" s="20"/>
     </row>
-    <row r="218" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A218" s="29" t="s">
         <v>736</v>
       </c>
@@ -30969,7 +30996,7 @@
       <c r="AN218" s="19"/>
       <c r="AO218" s="20"/>
     </row>
-    <row r="219" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A219" s="29" t="s">
         <v>739</v>
       </c>
@@ -31080,7 +31107,7 @@
       </c>
       <c r="AO219" s="20"/>
     </row>
-    <row r="220" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A220" s="29" t="s">
         <v>742</v>
       </c>
@@ -31189,7 +31216,7 @@
       <c r="AN220" s="19"/>
       <c r="AO220" s="20"/>
     </row>
-    <row r="221" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A221" s="29" t="s">
         <v>745</v>
       </c>
@@ -31298,7 +31325,7 @@
       <c r="AN221" s="19"/>
       <c r="AO221" s="20"/>
     </row>
-    <row r="222" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A222" s="29" t="s">
         <v>748</v>
       </c>
@@ -31407,7 +31434,7 @@
       <c r="AN222" s="19"/>
       <c r="AO222" s="20"/>
     </row>
-    <row r="223" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A223" s="29" t="s">
         <v>752</v>
       </c>
@@ -31516,7 +31543,7 @@
       <c r="AN223" s="19"/>
       <c r="AO223" s="20"/>
     </row>
-    <row r="224" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A224" s="29" t="s">
         <v>755</v>
       </c>
@@ -31625,7 +31652,7 @@
       <c r="AN224" s="19"/>
       <c r="AO224" s="20"/>
     </row>
-    <row r="225" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A225" s="29" t="s">
         <v>758</v>
       </c>
@@ -31734,7 +31761,7 @@
       <c r="AN225" s="19"/>
       <c r="AO225" s="20"/>
     </row>
-    <row r="226" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A226" s="29" t="s">
         <v>761</v>
       </c>
@@ -31845,7 +31872,7 @@
       </c>
       <c r="AO226" s="20"/>
     </row>
-    <row r="227" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A227" s="29" t="s">
         <v>764</v>
       </c>
@@ -31956,7 +31983,7 @@
       </c>
       <c r="AO227" s="20"/>
     </row>
-    <row r="228" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A228" s="29" t="s">
         <v>767</v>
       </c>
@@ -32067,7 +32094,7 @@
       </c>
       <c r="AO228" s="20"/>
     </row>
-    <row r="229" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A229" s="29" t="s">
         <v>770</v>
       </c>
@@ -32178,7 +32205,7 @@
       </c>
       <c r="AO229" s="20"/>
     </row>
-    <row r="230" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A230" s="29" t="s">
         <v>773</v>
       </c>
@@ -32287,7 +32314,7 @@
       <c r="AN230" s="19"/>
       <c r="AO230" s="20"/>
     </row>
-    <row r="231" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A231" s="29" t="s">
         <v>776</v>
       </c>
@@ -32396,7 +32423,7 @@
       <c r="AN231" s="19"/>
       <c r="AO231" s="20"/>
     </row>
-    <row r="232" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A232" s="29" t="s">
         <v>779</v>
       </c>
@@ -32505,7 +32532,7 @@
       <c r="AN232" s="19"/>
       <c r="AO232" s="20"/>
     </row>
-    <row r="233" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A233" s="29" t="s">
         <v>782</v>
       </c>
@@ -32616,7 +32643,7 @@
       </c>
       <c r="AO233" s="20"/>
     </row>
-    <row r="234" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A234" s="29" t="s">
         <v>785</v>
       </c>
@@ -32727,7 +32754,7 @@
       </c>
       <c r="AO234" s="20"/>
     </row>
-    <row r="235" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A235" s="29" t="s">
         <v>787</v>
       </c>
@@ -32838,7 +32865,7 @@
       </c>
       <c r="AO235" s="20"/>
     </row>
-    <row r="236" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A236" s="29" t="s">
         <v>790</v>
       </c>
@@ -32949,7 +32976,7 @@
       </c>
       <c r="AO236" s="20"/>
     </row>
-    <row r="237" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A237" s="29" t="s">
         <v>793</v>
       </c>
@@ -33060,7 +33087,7 @@
       </c>
       <c r="AO237" s="20"/>
     </row>
-    <row r="238" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A238" s="29" t="s">
         <v>796</v>
       </c>
@@ -33171,7 +33198,7 @@
       </c>
       <c r="AO238" s="20"/>
     </row>
-    <row r="239" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A239" s="29" t="s">
         <v>799</v>
       </c>
@@ -33282,7 +33309,7 @@
       </c>
       <c r="AO239" s="20"/>
     </row>
-    <row r="240" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A240" s="29" t="s">
         <v>803</v>
       </c>
@@ -33391,7 +33418,7 @@
       <c r="AN240" s="19"/>
       <c r="AO240" s="20"/>
     </row>
-    <row r="241" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A241" s="29" t="s">
         <v>806</v>
       </c>
@@ -33500,7 +33527,7 @@
       <c r="AN241" s="19"/>
       <c r="AO241" s="20"/>
     </row>
-    <row r="242" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A242" s="29" t="s">
         <v>809</v>
       </c>
@@ -33609,7 +33636,7 @@
       <c r="AN242" s="19"/>
       <c r="AO242" s="20"/>
     </row>
-    <row r="243" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A243" s="29" t="s">
         <v>812</v>
       </c>
@@ -33718,7 +33745,7 @@
       <c r="AN243" s="19"/>
       <c r="AO243" s="20"/>
     </row>
-    <row r="244" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A244" s="29" t="s">
         <v>816</v>
       </c>
@@ -33827,7 +33854,7 @@
       <c r="AN244" s="19"/>
       <c r="AO244" s="20"/>
     </row>
-    <row r="245" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A245" s="29" t="s">
         <v>819</v>
       </c>
@@ -33936,7 +33963,7 @@
       <c r="AN245" s="19"/>
       <c r="AO245" s="20"/>
     </row>
-    <row r="246" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A246" s="29" t="s">
         <v>822</v>
       </c>
@@ -34045,7 +34072,7 @@
       <c r="AN246" s="19"/>
       <c r="AO246" s="20"/>
     </row>
-    <row r="247" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A247" s="29" t="s">
         <v>825</v>
       </c>
@@ -34156,7 +34183,7 @@
       </c>
       <c r="AO247" s="20"/>
     </row>
-    <row r="248" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A248" s="29" t="s">
         <v>830</v>
       </c>
@@ -34265,7 +34292,7 @@
       <c r="AN248" s="23"/>
       <c r="AO248" s="20"/>
     </row>
-    <row r="249" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A249" s="29" t="s">
         <v>834</v>
       </c>
@@ -34376,7 +34403,7 @@
       </c>
       <c r="AO249" s="20"/>
     </row>
-    <row r="250" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A250" s="29" t="s">
         <v>838</v>
       </c>
@@ -34485,7 +34512,7 @@
       <c r="AN250" s="19"/>
       <c r="AO250" s="20"/>
     </row>
-    <row r="251" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A251" s="29" t="s">
         <v>841</v>
       </c>
@@ -34594,7 +34621,7 @@
       <c r="AN251" s="19"/>
       <c r="AO251" s="20"/>
     </row>
-    <row r="252" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A252" s="29" t="s">
         <v>844</v>
       </c>
@@ -34705,7 +34732,7 @@
       </c>
       <c r="AO252" s="20"/>
     </row>
-    <row r="253" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A253" s="29" t="s">
         <v>847</v>
       </c>
@@ -34816,7 +34843,7 @@
       </c>
       <c r="AO253" s="20"/>
     </row>
-    <row r="254" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A254" s="29" t="s">
         <v>849</v>
       </c>
@@ -34927,7 +34954,7 @@
       </c>
       <c r="AO254" s="20"/>
     </row>
-    <row r="255" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A255" s="29" t="s">
         <v>851</v>
       </c>
@@ -35036,7 +35063,7 @@
       <c r="AN255" s="19"/>
       <c r="AO255" s="20"/>
     </row>
-    <row r="256" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A256" s="29" t="s">
         <v>854</v>
       </c>
@@ -35147,7 +35174,7 @@
       </c>
       <c r="AO256" s="20"/>
     </row>
-    <row r="257" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A257" s="29" t="s">
         <v>857</v>
       </c>
@@ -35256,7 +35283,7 @@
       <c r="AN257" s="19"/>
       <c r="AO257" s="20"/>
     </row>
-    <row r="258" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A258" s="29" t="s">
         <v>861</v>
       </c>
@@ -35367,7 +35394,7 @@
       </c>
       <c r="AO258" s="20"/>
     </row>
-    <row r="259" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A259" s="29" t="s">
         <v>863</v>
       </c>
@@ -35480,7 +35507,7 @@
         <v>45491</v>
       </c>
     </row>
-    <row r="260" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A260" s="29" t="s">
         <v>866</v>
       </c>
@@ -35593,7 +35620,7 @@
         <v>45517</v>
       </c>
     </row>
-    <row r="261" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A261" s="29" t="s">
         <v>869</v>
       </c>
@@ -35702,7 +35729,7 @@
       <c r="AN261" s="19"/>
       <c r="AO261" s="36"/>
     </row>
-    <row r="262" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A262" s="29" t="s">
         <v>873</v>
       </c>
@@ -35813,7 +35840,7 @@
       </c>
       <c r="AO262" s="20"/>
     </row>
-    <row r="263" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A263" s="29" t="s">
         <v>877</v>
       </c>
@@ -35922,7 +35949,7 @@
       <c r="AN263" s="19"/>
       <c r="AO263" s="20"/>
     </row>
-    <row r="264" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A264" s="29" t="s">
         <v>880</v>
       </c>
@@ -36033,7 +36060,7 @@
       </c>
       <c r="AO264" s="20"/>
     </row>
-    <row r="265" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A265" s="29" t="s">
         <v>883</v>
       </c>
@@ -36146,7 +36173,7 @@
         <v>45571</v>
       </c>
     </row>
-    <row r="266" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A266" s="29" t="s">
         <v>886</v>
       </c>
@@ -36257,7 +36284,7 @@
       </c>
       <c r="AO266" s="20"/>
     </row>
-    <row r="267" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A267" s="29" t="s">
         <v>889</v>
       </c>
@@ -36370,7 +36397,7 @@
         <v>45571</v>
       </c>
     </row>
-    <row r="268" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A268" s="29" t="s">
         <v>892</v>
       </c>
@@ -36481,7 +36508,7 @@
         <v>45571</v>
       </c>
     </row>
-    <row r="269" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A269" s="29" t="s">
         <v>894</v>
       </c>
@@ -36598,7 +36625,7 @@
         <v>45571</v>
       </c>
     </row>
-    <row r="270" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A270" s="29" t="s">
         <v>897</v>
       </c>
@@ -36711,7 +36738,7 @@
         <v>45517</v>
       </c>
     </row>
-    <row r="271" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A271" s="29" t="s">
         <v>899</v>
       </c>
@@ -36824,7 +36851,7 @@
         <v>45517</v>
       </c>
     </row>
-    <row r="272" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A272" s="29" t="s">
         <v>901</v>
       </c>
@@ -36935,7 +36962,7 @@
       </c>
       <c r="AO272" s="20"/>
     </row>
-    <row r="273" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A273" s="29" t="s">
         <v>905</v>
       </c>
@@ -37046,7 +37073,7 @@
       </c>
       <c r="AO273" s="20"/>
     </row>
-    <row r="274" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A274" s="29" t="s">
         <v>909</v>
       </c>
@@ -37157,7 +37184,7 @@
       </c>
       <c r="AO274" s="20"/>
     </row>
-    <row r="275" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A275" s="29" t="s">
         <v>913</v>
       </c>
@@ -37268,7 +37295,7 @@
       </c>
       <c r="AO275" s="20"/>
     </row>
-    <row r="276" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A276" s="29" t="s">
         <v>916</v>
       </c>
@@ -37377,7 +37404,7 @@
       <c r="AN276" s="19"/>
       <c r="AO276" s="20"/>
     </row>
-    <row r="277" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A277" s="29" t="s">
         <v>919</v>
       </c>
@@ -37488,7 +37515,7 @@
       </c>
       <c r="AO277" s="20"/>
     </row>
-    <row r="278" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A278" s="29" t="s">
         <v>923</v>
       </c>
@@ -37597,7 +37624,7 @@
       <c r="AN278" s="19"/>
       <c r="AO278" s="20"/>
     </row>
-    <row r="279" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A279" s="29" t="s">
         <v>927</v>
       </c>
@@ -37706,7 +37733,7 @@
       <c r="AN279" s="19"/>
       <c r="AO279" s="20"/>
     </row>
-    <row r="280" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A280" s="29" t="s">
         <v>932</v>
       </c>
@@ -37817,7 +37844,7 @@
       </c>
       <c r="AO280" s="20"/>
     </row>
-    <row r="281" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A281" s="29" t="s">
         <v>936</v>
       </c>
@@ -37926,7 +37953,7 @@
       <c r="AN281" s="19"/>
       <c r="AO281" s="20"/>
     </row>
-    <row r="282" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A282" s="29" t="s">
         <v>939</v>
       </c>
@@ -38035,7 +38062,7 @@
       <c r="AN282" s="19"/>
       <c r="AO282" s="20"/>
     </row>
-    <row r="283" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A283" s="29" t="s">
         <v>942</v>
       </c>
@@ -38144,7 +38171,7 @@
       <c r="AN283" s="19"/>
       <c r="AO283" s="20"/>
     </row>
-    <row r="284" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A284" s="29" t="s">
         <v>945</v>
       </c>
@@ -38253,7 +38280,7 @@
       <c r="AN284" s="19"/>
       <c r="AO284" s="20"/>
     </row>
-    <row r="285" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A285" s="29" t="s">
         <v>948</v>
       </c>
@@ -38362,7 +38389,7 @@
       <c r="AN285" s="19"/>
       <c r="AO285" s="20"/>
     </row>
-    <row r="286" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A286" s="29" t="s">
         <v>952</v>
       </c>
@@ -38471,7 +38498,7 @@
       <c r="AN286" s="19"/>
       <c r="AO286" s="20"/>
     </row>
-    <row r="287" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A287" s="29" t="s">
         <v>955</v>
       </c>
@@ -38580,7 +38607,7 @@
       <c r="AN287" s="19"/>
       <c r="AO287" s="20"/>
     </row>
-    <row r="288" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A288" s="29" t="s">
         <v>957</v>
       </c>
@@ -38689,7 +38716,7 @@
       <c r="AN288" s="19"/>
       <c r="AO288" s="20"/>
     </row>
-    <row r="289" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A289" s="29" t="s">
         <v>961</v>
       </c>
@@ -38798,7 +38825,7 @@
       <c r="AN289" s="19"/>
       <c r="AO289" s="20"/>
     </row>
-    <row r="290" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A290" s="29" t="s">
         <v>964</v>
       </c>
@@ -38907,7 +38934,7 @@
       <c r="AN290" s="19"/>
       <c r="AO290" s="20"/>
     </row>
-    <row r="291" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A291" s="29" t="s">
         <v>968</v>
       </c>
@@ -39016,7 +39043,7 @@
       <c r="AN291" s="19"/>
       <c r="AO291" s="20"/>
     </row>
-    <row r="292" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A292" s="29" t="s">
         <v>971</v>
       </c>
@@ -39125,7 +39152,7 @@
       <c r="AN292" s="19"/>
       <c r="AO292" s="20"/>
     </row>
-    <row r="293" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A293" s="29" t="s">
         <v>974</v>
       </c>
@@ -39234,7 +39261,7 @@
       <c r="AN293" s="19"/>
       <c r="AO293" s="20"/>
     </row>
-    <row r="294" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A294" s="29" t="s">
         <v>977</v>
       </c>
@@ -39343,7 +39370,7 @@
       <c r="AN294" s="19"/>
       <c r="AO294" s="20"/>
     </row>
-    <row r="295" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A295" s="29" t="s">
         <v>980</v>
       </c>
@@ -39454,7 +39481,7 @@
       </c>
       <c r="AO295" s="20"/>
     </row>
-    <row r="296" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A296" s="29" t="s">
         <v>982</v>
       </c>
@@ -39565,7 +39592,7 @@
       </c>
       <c r="AO296" s="20"/>
     </row>
-    <row r="297" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A297" s="29" t="s">
         <v>985</v>
       </c>
@@ -39674,7 +39701,7 @@
       <c r="AN297" s="19"/>
       <c r="AO297" s="20"/>
     </row>
-    <row r="298" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A298" s="29" t="s">
         <v>988</v>
       </c>
@@ -39785,7 +39812,7 @@
       </c>
       <c r="AO298" s="20"/>
     </row>
-    <row r="299" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A299" s="29" t="s">
         <v>991</v>
       </c>
@@ -39896,7 +39923,7 @@
       </c>
       <c r="AO299" s="20"/>
     </row>
-    <row r="300" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A300" s="29" t="s">
         <v>993</v>
       </c>
@@ -40007,7 +40034,7 @@
       </c>
       <c r="AO300" s="20"/>
     </row>
-    <row r="301" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A301" s="29" t="s">
         <v>995</v>
       </c>
@@ -40116,7 +40143,7 @@
       <c r="AN301" s="19"/>
       <c r="AO301" s="20"/>
     </row>
-    <row r="302" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A302" s="29" t="s">
         <v>998</v>
       </c>
@@ -40225,7 +40252,7 @@
       <c r="AN302" s="19"/>
       <c r="AO302" s="20"/>
     </row>
-    <row r="303" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A303" s="29" t="s">
         <v>1001</v>
       </c>
@@ -40334,7 +40361,7 @@
       <c r="AN303" s="19"/>
       <c r="AO303" s="20"/>
     </row>
-    <row r="304" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A304" s="29" t="s">
         <v>1005</v>
       </c>
@@ -40443,7 +40470,7 @@
       <c r="AN304" s="19"/>
       <c r="AO304" s="20"/>
     </row>
-    <row r="305" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A305" s="29" t="s">
         <v>1008</v>
       </c>
@@ -40552,7 +40579,7 @@
       <c r="AN305" s="19"/>
       <c r="AO305" s="20"/>
     </row>
-    <row r="306" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A306" s="29" t="s">
         <v>1011</v>
       </c>
@@ -40663,7 +40690,7 @@
       </c>
       <c r="AO306" s="20"/>
     </row>
-    <row r="307" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A307" s="29" t="s">
         <v>1014</v>
       </c>
@@ -40772,7 +40799,7 @@
       <c r="AN307" s="19"/>
       <c r="AO307" s="20"/>
     </row>
-    <row r="308" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A308" s="29" t="s">
         <v>1017</v>
       </c>
@@ -40881,7 +40908,7 @@
       <c r="AN308" s="19"/>
       <c r="AO308" s="20"/>
     </row>
-    <row r="309" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A309" s="29" t="s">
         <v>1020</v>
       </c>
@@ -40990,7 +41017,7 @@
       <c r="AN309" s="19"/>
       <c r="AO309" s="20"/>
     </row>
-    <row r="310" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A310" s="29" t="s">
         <v>1023</v>
       </c>
@@ -41101,7 +41128,7 @@
       </c>
       <c r="AO310" s="20"/>
     </row>
-    <row r="311" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A311" s="29" t="s">
         <v>1026</v>
       </c>
@@ -41212,7 +41239,7 @@
       </c>
       <c r="AO311" s="20"/>
     </row>
-    <row r="312" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A312" s="29" t="s">
         <v>1029</v>
       </c>
@@ -41331,7 +41358,7 @@
       </c>
       <c r="AO312" s="20"/>
     </row>
-    <row r="313" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A313" s="29" t="s">
         <v>1033</v>
       </c>
@@ -41442,7 +41469,7 @@
       </c>
       <c r="AO313" s="20"/>
     </row>
-    <row r="314" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A314" s="29" t="s">
         <v>1037</v>
       </c>
@@ -41553,7 +41580,7 @@
       </c>
       <c r="AO314" s="20"/>
     </row>
-    <row r="315" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A315" s="29" t="s">
         <v>1040</v>
       </c>
@@ -41662,7 +41689,7 @@
       <c r="AN315" s="19"/>
       <c r="AO315" s="20"/>
     </row>
-    <row r="316" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A316" s="29" t="s">
         <v>1044</v>
       </c>
@@ -41771,7 +41798,7 @@
       <c r="AN316" s="19"/>
       <c r="AO316" s="20"/>
     </row>
-    <row r="317" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A317" s="29" t="s">
         <v>1048</v>
       </c>
@@ -41880,7 +41907,7 @@
       <c r="AN317" s="19"/>
       <c r="AO317" s="20"/>
     </row>
-    <row r="318" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A318" s="29" t="s">
         <v>1052</v>
       </c>
@@ -41989,7 +42016,7 @@
       <c r="AN318" s="19"/>
       <c r="AO318" s="20"/>
     </row>
-    <row r="319" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A319" s="29" t="s">
         <v>1055</v>
       </c>
@@ -42098,7 +42125,7 @@
       <c r="AN319" s="19"/>
       <c r="AO319" s="20"/>
     </row>
-    <row r="320" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A320" s="29" t="s">
         <v>1058</v>
       </c>
@@ -42207,7 +42234,7 @@
       <c r="AN320" s="19"/>
       <c r="AO320" s="20"/>
     </row>
-    <row r="321" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A321" s="29" t="s">
         <v>1061</v>
       </c>
@@ -42316,7 +42343,7 @@
       <c r="AN321" s="19"/>
       <c r="AO321" s="20"/>
     </row>
-    <row r="322" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A322" s="29" t="s">
         <v>1064</v>
       </c>
@@ -42425,7 +42452,7 @@
       <c r="AN322" s="19"/>
       <c r="AO322" s="20"/>
     </row>
-    <row r="323" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A323" s="29" t="s">
         <v>1066</v>
       </c>
@@ -42534,7 +42561,7 @@
       <c r="AN323" s="19"/>
       <c r="AO323" s="20"/>
     </row>
-    <row r="324" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A324" s="29" t="s">
         <v>1069</v>
       </c>
@@ -42643,7 +42670,7 @@
       <c r="AN324" s="19"/>
       <c r="AO324" s="20"/>
     </row>
-    <row r="325" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A325" s="29" t="s">
         <v>1072</v>
       </c>
@@ -42752,7 +42779,7 @@
       <c r="AN325" s="19"/>
       <c r="AO325" s="20"/>
     </row>
-    <row r="326" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A326" s="29" t="s">
         <v>1075</v>
       </c>
@@ -42861,7 +42888,7 @@
       <c r="AN326" s="19"/>
       <c r="AO326" s="20"/>
     </row>
-    <row r="327" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A327" s="29" t="s">
         <v>1079</v>
       </c>
@@ -42970,7 +42997,7 @@
       <c r="AN327" s="19"/>
       <c r="AO327" s="20"/>
     </row>
-    <row r="328" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A328" s="29" t="s">
         <v>1083</v>
       </c>
@@ -43079,7 +43106,7 @@
       <c r="AN328" s="19"/>
       <c r="AO328" s="20"/>
     </row>
-    <row r="329" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A329" s="29" t="s">
         <v>1087</v>
       </c>
@@ -43188,7 +43215,7 @@
       <c r="AN329" s="19"/>
       <c r="AO329" s="20"/>
     </row>
-    <row r="330" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A330" s="29" t="s">
         <v>1089</v>
       </c>
@@ -43297,7 +43324,7 @@
       <c r="AN330" s="19"/>
       <c r="AO330" s="20"/>
     </row>
-    <row r="331" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A331" s="29" t="s">
         <v>1091</v>
       </c>
@@ -43406,7 +43433,7 @@
       <c r="AN331" s="19"/>
       <c r="AO331" s="20"/>
     </row>
-    <row r="332" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A332" s="29" t="s">
         <v>1094</v>
       </c>
@@ -43515,7 +43542,7 @@
       <c r="AN332" s="19"/>
       <c r="AO332" s="20"/>
     </row>
-    <row r="333" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A333" s="29" t="s">
         <v>1096</v>
       </c>
@@ -43624,7 +43651,7 @@
       <c r="AN333" s="19"/>
       <c r="AO333" s="20"/>
     </row>
-    <row r="334" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A334" s="29" t="s">
         <v>1099</v>
       </c>
@@ -43733,7 +43760,7 @@
       <c r="AN334" s="19"/>
       <c r="AO334" s="20"/>
     </row>
-    <row r="335" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A335" s="29" t="s">
         <v>1101</v>
       </c>
@@ -43842,7 +43869,7 @@
       <c r="AN335" s="19"/>
       <c r="AO335" s="20"/>
     </row>
-    <row r="336" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A336" s="29" t="s">
         <v>1104</v>
       </c>
@@ -43951,7 +43978,7 @@
       <c r="AN336" s="19"/>
       <c r="AO336" s="20"/>
     </row>
-    <row r="337" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A337" s="29" t="s">
         <v>1107</v>
       </c>
@@ -44060,7 +44087,7 @@
       <c r="AN337" s="19"/>
       <c r="AO337" s="20"/>
     </row>
-    <row r="338" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A338" s="29" t="s">
         <v>1109</v>
       </c>
@@ -44169,7 +44196,7 @@
       <c r="AN338" s="19"/>
       <c r="AO338" s="20"/>
     </row>
-    <row r="339" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A339" s="29" t="s">
         <v>1111</v>
       </c>
@@ -44278,7 +44305,7 @@
       <c r="AN339" s="19"/>
       <c r="AO339" s="20"/>
     </row>
-    <row r="340" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A340" s="29" t="s">
         <v>1114</v>
       </c>
@@ -44387,7 +44414,7 @@
       <c r="AN340" s="19"/>
       <c r="AO340" s="20"/>
     </row>
-    <row r="341" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A341" s="29" t="s">
         <v>1117</v>
       </c>
@@ -44496,7 +44523,7 @@
       <c r="AN341" s="19"/>
       <c r="AO341" s="20"/>
     </row>
-    <row r="342" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A342" s="29" t="s">
         <v>1120</v>
       </c>
@@ -44605,7 +44632,7 @@
       <c r="AN342" s="19"/>
       <c r="AO342" s="20"/>
     </row>
-    <row r="343" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A343" s="29" t="s">
         <v>1123</v>
       </c>
@@ -44714,7 +44741,7 @@
       <c r="AN343" s="19"/>
       <c r="AO343" s="20"/>
     </row>
-    <row r="344" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A344" s="29" t="s">
         <v>1126</v>
       </c>
@@ -44823,7 +44850,7 @@
       <c r="AN344" s="19"/>
       <c r="AO344" s="20"/>
     </row>
-    <row r="345" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A345" s="29" t="s">
         <v>1128</v>
       </c>
@@ -44932,7 +44959,7 @@
       <c r="AN345" s="19"/>
       <c r="AO345" s="20"/>
     </row>
-    <row r="346" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A346" s="29" t="s">
         <v>1131</v>
       </c>
@@ -45041,7 +45068,7 @@
       <c r="AN346" s="19"/>
       <c r="AO346" s="20"/>
     </row>
-    <row r="347" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A347" s="29" t="s">
         <v>1134</v>
       </c>
@@ -45150,7 +45177,7 @@
       <c r="AN347" s="19"/>
       <c r="AO347" s="20"/>
     </row>
-    <row r="348" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A348" s="29" t="s">
         <v>1137</v>
       </c>
@@ -45259,7 +45286,7 @@
       <c r="AN348" s="19"/>
       <c r="AO348" s="20"/>
     </row>
-    <row r="349" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A349" s="29" t="s">
         <v>1140</v>
       </c>
@@ -45368,7 +45395,7 @@
       <c r="AN349" s="19"/>
       <c r="AO349" s="20"/>
     </row>
-    <row r="350" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A350" s="29" t="s">
         <v>1143</v>
       </c>
@@ -45477,7 +45504,7 @@
       <c r="AN350" s="19"/>
       <c r="AO350" s="20"/>
     </row>
-    <row r="351" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A351" s="29" t="s">
         <v>1146</v>
       </c>
@@ -45586,7 +45613,7 @@
       <c r="AN351" s="19"/>
       <c r="AO351" s="20"/>
     </row>
-    <row r="352" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A352" s="29" t="s">
         <v>1149</v>
       </c>
@@ -45695,7 +45722,7 @@
       <c r="AN352" s="19"/>
       <c r="AO352" s="20"/>
     </row>
-    <row r="353" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A353" s="29" t="s">
         <v>1152</v>
       </c>
@@ -45808,7 +45835,7 @@
         <v>45491</v>
       </c>
     </row>
-    <row r="354" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A354" s="29" t="s">
         <v>1156</v>
       </c>
@@ -45919,7 +45946,7 @@
       </c>
       <c r="AO354" s="20"/>
     </row>
-    <row r="355" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A355" s="29" t="s">
         <v>1158</v>
       </c>
@@ -46030,7 +46057,7 @@
       </c>
       <c r="AO355" s="20"/>
     </row>
-    <row r="356" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A356" s="29" t="s">
         <v>1162</v>
       </c>
@@ -46139,7 +46166,7 @@
       <c r="AN356" s="19"/>
       <c r="AO356" s="20"/>
     </row>
-    <row r="357" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A357" s="29" t="s">
         <v>1164</v>
       </c>
@@ -46248,7 +46275,7 @@
       <c r="AN357" s="19"/>
       <c r="AO357" s="20"/>
     </row>
-    <row r="358" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A358" s="29" t="s">
         <v>1166</v>
       </c>
@@ -46357,7 +46384,7 @@
       <c r="AN358" s="19"/>
       <c r="AO358" s="20"/>
     </row>
-    <row r="359" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A359" s="29" t="s">
         <v>1170</v>
       </c>
@@ -46466,7 +46493,7 @@
       <c r="AN359" s="19"/>
       <c r="AO359" s="20"/>
     </row>
-    <row r="360" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A360" s="29" t="s">
         <v>1173</v>
       </c>
@@ -46575,7 +46602,7 @@
       <c r="AN360" s="19"/>
       <c r="AO360" s="20"/>
     </row>
-    <row r="361" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A361" s="29" t="s">
         <v>1176</v>
       </c>
@@ -46684,7 +46711,7 @@
       <c r="AN361" s="19"/>
       <c r="AO361" s="20"/>
     </row>
-    <row r="362" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A362" s="29" t="s">
         <v>1179</v>
       </c>
@@ -46793,7 +46820,7 @@
       <c r="AN362" s="19"/>
       <c r="AO362" s="20"/>
     </row>
-    <row r="363" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A363" s="29" t="s">
         <v>1183</v>
       </c>
@@ -46904,7 +46931,7 @@
       </c>
       <c r="AO363" s="20"/>
     </row>
-    <row r="364" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A364" s="29" t="s">
         <v>1186</v>
       </c>
@@ -47013,7 +47040,7 @@
       <c r="AN364" s="19"/>
       <c r="AO364" s="20"/>
     </row>
-    <row r="365" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A365" s="29" t="s">
         <v>1190</v>
       </c>
@@ -47122,7 +47149,7 @@
       <c r="AN365" s="19"/>
       <c r="AO365" s="20"/>
     </row>
-    <row r="366" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A366" s="29" t="s">
         <v>1193</v>
       </c>
@@ -47231,7 +47258,7 @@
       <c r="AN366" s="19"/>
       <c r="AO366" s="20"/>
     </row>
-    <row r="367" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A367" s="29" t="s">
         <v>1197</v>
       </c>
@@ -47342,7 +47369,7 @@
       </c>
       <c r="AO367" s="20"/>
     </row>
-    <row r="368" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A368" s="29" t="s">
         <v>1200</v>
       </c>
@@ -47453,7 +47480,7 @@
       </c>
       <c r="AO368" s="20"/>
     </row>
-    <row r="369" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A369" s="29" t="s">
         <v>1203</v>
       </c>
@@ -47562,7 +47589,7 @@
       <c r="AN369" s="19"/>
       <c r="AO369" s="20"/>
     </row>
-    <row r="370" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A370" s="29" t="s">
         <v>1206</v>
       </c>
@@ -47671,7 +47698,7 @@
       <c r="AN370" s="19"/>
       <c r="AO370" s="20"/>
     </row>
-    <row r="371" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A371" s="29" t="s">
         <v>1209</v>
       </c>
@@ -47780,7 +47807,7 @@
       <c r="AN371" s="19"/>
       <c r="AO371" s="20"/>
     </row>
-    <row r="372" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A372" s="29" t="s">
         <v>1212</v>
       </c>
@@ -47889,7 +47916,7 @@
       <c r="AN372" s="19"/>
       <c r="AO372" s="20"/>
     </row>
-    <row r="373" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A373" s="29" t="s">
         <v>1215</v>
       </c>
@@ -47998,7 +48025,7 @@
       <c r="AN373" s="19"/>
       <c r="AO373" s="20"/>
     </row>
-    <row r="374" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A374" s="29" t="s">
         <v>1219</v>
       </c>
@@ -48107,7 +48134,7 @@
       <c r="AN374" s="19"/>
       <c r="AO374" s="20"/>
     </row>
-    <row r="375" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A375" s="29" t="s">
         <v>1223</v>
       </c>
@@ -48216,7 +48243,7 @@
       <c r="AN375" s="19"/>
       <c r="AO375" s="20"/>
     </row>
-    <row r="376" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A376" s="29" t="s">
         <v>1226</v>
       </c>
@@ -48325,7 +48352,7 @@
       <c r="AN376" s="19"/>
       <c r="AO376" s="20"/>
     </row>
-    <row r="377" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A377" s="29" t="s">
         <v>1229</v>
       </c>
@@ -48434,7 +48461,7 @@
       <c r="AN377" s="19"/>
       <c r="AO377" s="20"/>
     </row>
-    <row r="378" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A378" s="29" t="s">
         <v>1231</v>
       </c>
@@ -48543,7 +48570,7 @@
       <c r="AN378" s="19"/>
       <c r="AO378" s="20"/>
     </row>
-    <row r="379" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A379" s="29" t="s">
         <v>1234</v>
       </c>
@@ -48652,7 +48679,7 @@
       <c r="AN379" s="19"/>
       <c r="AO379" s="20"/>
     </row>
-    <row r="380" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A380" s="29" t="s">
         <v>1236</v>
       </c>
@@ -48761,7 +48788,7 @@
       <c r="AN380" s="19"/>
       <c r="AO380" s="20"/>
     </row>
-    <row r="381" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A381" s="29" t="s">
         <v>1238</v>
       </c>
@@ -48870,7 +48897,7 @@
       <c r="AN381" s="19"/>
       <c r="AO381" s="20"/>
     </row>
-    <row r="382" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A382" s="29" t="s">
         <v>1241</v>
       </c>
@@ -48979,7 +49006,7 @@
       <c r="AN382" s="19"/>
       <c r="AO382" s="20"/>
     </row>
-    <row r="383" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A383" s="29" t="s">
         <v>1245</v>
       </c>
@@ -49088,7 +49115,7 @@
       <c r="AN383" s="19"/>
       <c r="AO383" s="20"/>
     </row>
-    <row r="384" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A384" s="29" t="s">
         <v>1248</v>
       </c>
@@ -49197,7 +49224,7 @@
       <c r="AN384" s="19"/>
       <c r="AO384" s="20"/>
     </row>
-    <row r="385" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A385" s="29" t="s">
         <v>1250</v>
       </c>
@@ -49306,7 +49333,7 @@
       <c r="AN385" s="19"/>
       <c r="AO385" s="20"/>
     </row>
-    <row r="386" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A386" s="29" t="s">
         <v>1253</v>
       </c>
@@ -49415,7 +49442,7 @@
       <c r="AN386" s="19"/>
       <c r="AO386" s="20"/>
     </row>
-    <row r="387" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A387" s="29" t="s">
         <v>1257</v>
       </c>
@@ -49524,7 +49551,7 @@
       <c r="AN387" s="19"/>
       <c r="AO387" s="20"/>
     </row>
-    <row r="388" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A388" s="37" t="s">
         <v>1259</v>
       </c>
@@ -49635,7 +49662,7 @@
       <c r="AN388" s="24"/>
       <c r="AO388" s="20"/>
     </row>
-    <row r="389" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A389" s="29" t="s">
         <v>1265</v>
       </c>
@@ -49817,18 +49844,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EEFFBB1-1A6E-4B61-8EC8-F3DF1FA46298}">
   <dimension ref="A1:F95"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36.6640625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="54.77734375" style="7" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="71.109375" style="7" customWidth="1"/>
-    <col min="5" max="5" width="52.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="64.44140625" style="7" customWidth="1"/>
-    <col min="7" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="36.6328125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="54.81640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="22.08984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="71.08984375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="52.453125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="64.453125" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>1267</v>
       </c>
@@ -49848,7 +49875,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
@@ -49868,7 +49895,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
@@ -49888,7 +49915,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
@@ -49908,7 +49935,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
         <v>3</v>
       </c>
@@ -49926,7 +49953,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
         <v>4</v>
       </c>
@@ -49944,7 +49971,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
@@ -49964,7 +49991,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
         <v>6</v>
       </c>
@@ -49982,7 +50009,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="62" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
         <v>7</v>
       </c>
@@ -50002,7 +50029,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="62" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
         <v>8</v>
       </c>
@@ -50022,7 +50049,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="62" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
         <v>9</v>
       </c>
@@ -50042,7 +50069,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
         <v>10</v>
       </c>
@@ -50062,7 +50089,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A13" s="10" t="s">
         <v>11</v>
       </c>
@@ -50082,7 +50109,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="78" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="62" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
         <v>12</v>
       </c>
@@ -50100,7 +50127,7 @@
       </c>
       <c r="F14" s="14"/>
     </row>
-    <row r="15" spans="1:6" ht="78" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="62" x14ac:dyDescent="0.35">
       <c r="A15" s="10" t="s">
         <v>13</v>
       </c>
@@ -50118,7 +50145,7 @@
       </c>
       <c r="F15" s="14"/>
     </row>
-    <row r="16" spans="1:6" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
         <v>14</v>
       </c>
@@ -50136,7 +50163,7 @@
       </c>
       <c r="F16" s="14"/>
     </row>
-    <row r="17" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A17" s="10" t="s">
         <v>15</v>
       </c>
@@ -50154,7 +50181,7 @@
       </c>
       <c r="F17" s="14"/>
     </row>
-    <row r="18" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
         <v>16</v>
       </c>
@@ -50172,7 +50199,7 @@
       </c>
       <c r="F18" s="14"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="10" t="s">
         <v>17</v>
       </c>
@@ -50188,7 +50215,7 @@
       </c>
       <c r="F19" s="14"/>
     </row>
-    <row r="20" spans="1:6" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A20" s="10" t="s">
         <v>18</v>
       </c>
@@ -50206,7 +50233,7 @@
       </c>
       <c r="F20" s="14"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="10" t="s">
         <v>19</v>
       </c>
@@ -50224,7 +50251,7 @@
       </c>
       <c r="F21" s="14"/>
     </row>
-    <row r="22" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A22" s="10" t="s">
         <v>20</v>
       </c>
@@ -50242,7 +50269,7 @@
       </c>
       <c r="F22" s="14"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="10" t="s">
         <v>21</v>
       </c>
@@ -50260,7 +50287,7 @@
       </c>
       <c r="F23" s="14"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="10" t="s">
         <v>22</v>
       </c>
@@ -50276,7 +50303,7 @@
       </c>
       <c r="F24" s="14"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="10" t="s">
         <v>23</v>
       </c>
@@ -50292,7 +50319,7 @@
       </c>
       <c r="F25" s="14"/>
     </row>
-    <row r="26" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
         <v>24</v>
       </c>
@@ -50310,7 +50337,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A27" s="10" t="s">
         <v>25</v>
       </c>
@@ -50330,7 +50357,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A28" s="10" t="s">
         <v>26</v>
       </c>
@@ -50350,7 +50377,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A29" s="10" t="s">
         <v>27</v>
       </c>
@@ -50370,7 +50397,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="33" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
         <v>28</v>
       </c>
@@ -50390,7 +50417,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A31" s="10" t="s">
         <v>29</v>
       </c>
@@ -50410,7 +50437,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
         <v>30</v>
       </c>
@@ -50430,7 +50457,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A33" s="10" t="s">
         <v>31</v>
       </c>
@@ -50450,7 +50477,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A34" s="10" t="s">
         <v>32</v>
       </c>
@@ -50470,7 +50497,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="10" t="s">
         <v>33</v>
       </c>
@@ -50488,7 +50515,7 @@
       </c>
       <c r="F35" s="14"/>
     </row>
-    <row r="36" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A36" s="10" t="s">
         <v>34</v>
       </c>
@@ -50508,7 +50535,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A37" s="10" t="s">
         <v>35</v>
       </c>
@@ -50528,7 +50555,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="10" t="s">
         <v>36</v>
       </c>
@@ -50548,7 +50575,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A39" s="10" t="s">
         <v>37</v>
       </c>
@@ -50568,7 +50595,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A40" s="10" t="s">
         <v>1409</v>
       </c>
@@ -50588,7 +50615,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="10" t="s">
         <v>1406</v>
       </c>
@@ -50608,7 +50635,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>1365</v>
       </c>
@@ -50616,7 +50643,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
         <v>47</v>
       </c>
@@ -50624,7 +50651,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
         <v>1368</v>
       </c>
@@ -50632,10 +50659,10 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="15"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
         <v>1370</v>
       </c>
@@ -50643,7 +50670,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A48" s="11" t="s">
         <v>1372</v>
       </c>
@@ -50651,7 +50678,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A49" s="11" t="s">
         <v>1374</v>
       </c>
@@ -50659,7 +50686,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A50" s="11" t="s">
         <v>1376</v>
       </c>
@@ -50667,7 +50694,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="11" t="s">
         <v>1378</v>
       </c>
@@ -50675,7 +50702,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="11" t="s">
         <v>1380</v>
       </c>
@@ -50683,7 +50710,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="11" t="s">
         <v>1382</v>
       </c>
@@ -50691,7 +50718,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A54" s="11" t="s">
         <v>1384</v>
       </c>
@@ -50699,7 +50726,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="11" t="s">
         <v>1386</v>
       </c>
@@ -50708,7 +50735,7 @@
       </c>
       <c r="C55" s="3"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="11" t="s">
         <v>1388</v>
       </c>
@@ -50716,7 +50743,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
         <v>1390</v>
       </c>
@@ -50724,7 +50751,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="9" t="s">
         <v>1392</v>
       </c>
@@ -50732,7 +50759,7 @@
         <v>181844</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
         <v>1393</v>
       </c>
@@ -50740,112 +50767,112 @@
         <v>388</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
         <v>1394</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="44" t="s">
         <v>1395</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="45"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" s="45"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" s="45"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" s="45"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" s="45"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" s="46"/>
     </row>
-    <row r="70" spans="1:1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="44" t="s">
         <v>1396</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" s="45"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" s="45"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" s="45"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" s="45"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" s="45"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" s="45"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" s="45"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" s="45"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" s="45"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" s="45"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="45"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="45"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="45"/>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="45"/>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="45"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="45"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="45"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="45"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="45"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="45"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="45"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="45"/>
     </row>
-    <row r="93" spans="1:2" ht="87" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" ht="87" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="46"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="12"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="12"/>
       <c r="B95" s="16"/>
     </row>
@@ -50906,15 +50933,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C7734E9F98CDED40B2A2459939C03A36" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="714d4ddb00860fb80f0b4a54262f2f80">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2624f4f0-6830-48b6-9c21-80b2613400ca" xmlns:ns3="d337210d-25f7-4ced-91e1-19a0946fcb25" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5ce1e1c79ebbab3f68054ecb3b8d007b" ns2:_="" ns3:_="">
     <xsd:import namespace="2624f4f0-6830-48b6-9c21-80b2613400ca"/>
@@ -51145,6 +51163,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15821E26-0416-43DF-8894-FB2498CD7580}">
   <ds:schemaRefs>
@@ -51163,14 +51190,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0E9CFC5-E3D9-4ED1-BD0E-6DB50CB80DD6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BB49D39-0E65-411C-B5F6-D9EAEB639B61}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -51187,4 +51206,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0E9CFC5-E3D9-4ED1-BD0E-6DB50CB80DD6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>